--- a/output/quickfixclose18_portfolio_daily.xlsx
+++ b/output/quickfixclose18_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>230,756.86</t>
+          <t>246,414.20</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+130.76%</t>
+          <t>+146.41%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>237,851  (+137.85%)</t>
+          <t>254,001  (+154.00%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,939  (7.1 pts of return)</t>
+          <t>3,969  (7.6 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5.7x</t>
+          <t>6.4x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6.0 bars</t>
+          <t>6.1 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+12.08R  (best +41.64R)</t>
+          <t>+11.97R  (best +41.64R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13,004  (+12.08%)</t>
+          <t>13,159  (+11.97%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5759,22 +5759,74 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>230756.86</v>
+        <v>230904.15</v>
       </c>
       <c r="C186" s="5" t="n">
+        <v>7829.1</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>223075.05</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>246531.56</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>6302.28</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>240229.27</v>
+      </c>
+      <c r="E187" t="n">
+        <v>3</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures exit_close (+15,627)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>246414.2</v>
+      </c>
+      <c r="C188" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D186" s="5" t="n">
-        <v>230756.86</v>
-      </c>
-      <c r="E186" t="n">
+      <c r="D188" s="5" t="n">
+        <v>246414.2</v>
+      </c>
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -9563,14 +9615,22 @@
           <t>2026-07-08</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>18</v>
+      </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>10.274</v>
       </c>
       <c r="G74" t="n">
-        <v>0.02</v>
+        <v>0.039</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.02</v>
+        <v>10.235</v>
       </c>
       <c r="I74" s="5" t="n">
         <v>161905.37</v>
@@ -9578,15 +9638,15 @@
       <c r="J74" s="5" t="n">
         <v>2250.48</v>
       </c>
-      <c r="K74" s="6" t="n">
-        <v>-44.13</v>
+      <c r="K74" s="7" t="n">
+        <v>23034.35</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>281088.36</v>
+        <v>304314.2</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>exit_close</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9685,7 @@
         <v>-63.89</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>281215.97</v>
+        <v>304250.32</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -9668,7 +9728,7 @@
         <v>-83.48</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>281132.49</v>
+        <v>304166.84</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9711,7 +9771,7 @@
         <v>-46.11</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>281042.25</v>
+        <v>304120.73</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>

--- a/output/quickfixclose18_portfolio_daily.xlsx
+++ b/output/quickfixclose18_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>246,414.20</t>
+          <t>246,401.25</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+146.41%</t>
+          <t>+146.40%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,969  (7.6 pts of return)</t>
+          <t>3,982  (7.6 pts of return)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5811,22 +5811,78 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>246414.2</v>
+        <v>246531.56</v>
       </c>
       <c r="C188" s="5" t="n">
+        <v>6302.28</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>240229.27</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>246531.56</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>13437.33</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>233094.22</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 2,402); Nasdaq_100_E_mini short (risk 2,378); S_P_500_E_mini short (risk 2,354)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>246401.25</v>
+      </c>
+      <c r="C190" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D188" s="5" t="n">
-        <v>246414.2</v>
-      </c>
-      <c r="E188" t="n">
+      <c r="D190" s="5" t="n">
+        <v>246401.25</v>
+      </c>
+      <c r="E190" t="n">
         <v>0</v>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,331)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9771,9 +9827,181 @@
         <v>-46.11</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>304120.73</v>
+        <v>304098.79</v>
       </c>
       <c r="M77" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>293900.25</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>4085.21</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>-14.18</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>304145.74</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>289815.03</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>4028.43</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>304159.92</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>285786.61</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>3972.43</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>304144.9</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>281814.17</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>3917.22</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>304160.14</v>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>

--- a/output/quickfixclose18_portfolio_daily.xlsx
+++ b/output/quickfixclose18_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>246,401.25</t>
+          <t>244,043.16</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+146.40%</t>
+          <t>+144.04%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>254,001  (+154.00%)</t>
+          <t>251,600  (+151.60%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,982  (7.6 pts of return)</t>
+          <t>4,009  (7.6 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6.4x</t>
+          <t>6.3x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,378  (-1.28%)</t>
+          <t>-1,395  (-1.28%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5863,26 +5863,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>246401.25</v>
+        <v>246531.56</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>15768.28</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>230763.28</v>
+      </c>
+      <c r="E190" t="n">
+        <v>7</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,331)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>244043.16</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>246401.25</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>244043.16</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 2,331)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 2,308); NY_Palladium_Futures short (risk 2,285)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX stop (-2,347); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9827,7 +9855,7 @@
         <v>-46.11</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>304098.79</v>
+        <v>300136.1</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9870,7 +9898,7 @@
         <v>-14.18</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>304145.74</v>
+        <v>300183.05</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9913,7 +9941,7 @@
         <v>-0.22</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>304159.92</v>
+        <v>300222.62</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9956,7 +9984,7 @@
         <v>-0.84</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>304144.9</v>
+        <v>300182.21</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9980,14 +10008,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>281814.17</v>
@@ -9996,12 +10032,98 @@
         <v>3917.22</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>-6.7</v>
+        <v>-3944</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>304160.14</v>
+        <v>300222.84</v>
       </c>
       <c r="M81" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>277896.95</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>3862.77</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>-10.44</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>300212.18</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>274034.19</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>3809.08</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>-14.94</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>300197.24</v>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
